--- a/recipes/onion-garlic-free-indian/focus-states/07-manipur/excel/manipur-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/07-manipur/excel/manipur-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sesame Eromba</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sesame Eromba</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Side  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -1728,13 +1731,13 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Pound roasted sesame and chilli to a coarse paste in a stone mortar or crush in a steel bowl.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
@@ -1746,44 +1749,210 @@
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>Mash potatoes and beans with the paste, salt and mustard oil. Keep some texture.</t>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
         </is>
       </c>
       <c r="C23" s="31" t="n"/>
       <c r="D23" s="31" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="42" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Serve at room temperature as a side to rice and stew.</t>
+          <t>Pound roasted sesame and chilli to a coarse paste in a stone mortar or crush in a steel bowl.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Mash potatoes and beans with the paste, salt and mustard oil. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Keep some texture. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Serve at room temperature as a side to rice and stew. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 272  ·  Protein 11 g  ·  Carbs 38 g  ·  Fat 9 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Sesame · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Sesame Eromba: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Sesame; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1797,7 +1966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1809,7 +1978,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Yongchak Veg (parkia)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Yongchak Veg (parkia)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1819,7 +1988,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Side  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1839,44 +2008,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2042,48 +2211,227 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Heat mustard oil in a steel kadhai. Add ginger and chilli.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>Add beans and salt. Stir-fry 10–12 minutes until tender with a little bite.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="31" t="n"/>
     </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Heat mustard oil in a steel kadhai. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Add ginger and chilli. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Add beans and salt. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Stir-fry 10–12 minutes until tender with a little bite. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 275  ·  Protein 13 g  ·  Carbs 39 g  ·  Fat 8 g  ·  Fibre 10 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Yongchak Veg (parkia): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2097,7 +2445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2109,7 +2457,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Boiled Seasonal Beans</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Boiled Seasonal Beans</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2119,7 +2467,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Side  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2139,44 +2487,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -2342,13 +2690,13 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Boil beans in salted water with ginger and chilli for 8–10 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
@@ -2360,30 +2708,209 @@
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>Drain. Toss with a spoon of the cooking liquor. Serve hot.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="31" t="n"/>
     </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Boil beans in salted water with ginger and chilli for 8–10 minutes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Drain. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Toss with a spoon of the cooking liquor. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Serve hot. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 252  ·  Protein 16 g  ·  Carbs 46 g  ·  Fat 1 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Boiled Seasonal Beans: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2397,7 +2924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2409,7 +2936,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Steamed Sticky Rice</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Steamed Sticky Rice</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2419,7 +2946,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Bread  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2439,44 +2966,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 5 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -2606,13 +3133,13 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Rinse rice. Soak in water 4 hours or overnight. Drain.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
@@ -2624,41 +3151,246 @@
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>Steam in a stainless steel steamer 20–25 minutes until translucent and sticky.</t>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
         </is>
       </c>
       <c r="C20" s="31" t="n"/>
       <c r="D20" s="31" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Fluff with a fork. Serve with chamthong or ooti. Never aluminium.</t>
+          <t>Rinse rice. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Soak in water 4 hours or overnight. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Drain. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Steam in a stainless steel steamer 20–25 minutes until translucent and sticky. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Fluff with a fork. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Serve with chamthong or ooti. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Never aluminium. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 360  ·  Protein 7 g  ·  Carbs 79 g  ·  Fat 1 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Steamed Sticky Rice: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="32">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2672,7 +3404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2684,7 +3416,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chak-Hao Rice</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chak-Hao Rice</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2694,7 +3426,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Bread  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2714,44 +3446,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 5 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -2881,13 +3613,13 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Rinse until the water runs less purple. Soak 2 hours. Drain.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
@@ -2899,41 +3631,233 @@
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>Steam or simmer in steel with salt until grains are tender, 25–30 minutes.</t>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
         </is>
       </c>
       <c r="C20" s="31" t="n"/>
       <c r="D20" s="31" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Rest 5 minutes. The rice should be nutty and slightly chewy.</t>
+          <t>Rinse until the water runs less purple. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Soak 2 hours. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Drain. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Steam or simmer in steel with salt until grains are tender, 25–30 minutes. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Rest 5 minutes. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>The rice should be nutty and slightly chewy. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 270  ·  Protein 5 g  ·  Carbs 59 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Chak-Hao Rice: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="31">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2947,7 +3871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2959,7 +3883,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Soft Roti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Soft Roti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2969,7 +3893,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Bread  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2989,44 +3913,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3174,13 +4098,13 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Knead atta, salt and water 5 minutes. Rest 10 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
@@ -3192,42 +4116,260 @@
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>Divide into 8 balls. Roll 15 cm discs. Cook on a cast-iron tawa until they puff.</t>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
         </is>
       </c>
       <c r="C21" s="31" t="n"/>
       <c r="D21" s="31" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Brush with ghee. Keep wrapped in a cloth.</t>
+          <t>Heat fat in Cast-iron tawa (not aluminium) on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Knead atta, salt and water 5 minutes. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Rest 10 minutes. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Divide into 8 balls. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Roll 15 cm discs. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook on a cast-iron tawa until they puff. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Brush with ghee. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Keep wrapped in a cloth. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 261  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 2 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Soft Roti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="34">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3241,7 +4383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3253,7 +4395,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Til-Gud Ladoo</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Til-Gud Ladoo</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3263,7 +4405,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Sweet  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3283,44 +4425,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3468,60 +4610,239 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Melt jaggery with ghee in a steel kadhai until it forms a soft ball in cold water.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>Stir in sesame and cardamom. Off the heat, shape 12 ladoos while warm.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C21" s="31" t="n"/>
       <c r="D21" s="31" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Cool on a steel plate. Store in an airtight tin.</t>
+          <t>Melt jaggery with ghee in a steel kadhai until it forms a soft ball in cold water.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Stir in sesame and cardamom. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Off the heat, shape 12 ladoos while warm. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cool on a steel plate. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Store in an airtight tin. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 362  ·  Protein 7 g  ·  Carbs 38 g  ·  Fat 22 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Til-Gud Ladoo: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3535,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3547,7 +4868,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Steamed Rice Cake</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Steamed Rice Cake</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3557,7 +4878,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Sweet  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3577,44 +4898,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3798,13 +5119,13 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Mix rice flour, jaggery, coconut, salt, cardamom and water to a thick batter.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
@@ -3816,44 +5137,223 @@
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>Spoon into a steel idli mould or thali. Steam 12–15 minutes.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C23" s="31" t="n"/>
       <c r="D23" s="31" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Unmould. Serve warm.</t>
+          <t>Mix rice flour, jaggery, coconut, salt, cardamom and water to a thick batter. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Spoon into a steel idli mould or thali. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Steam 12–15 minutes. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Unmould. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Serve warm. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 347  ·  Protein 4 g  ·  Carbs 67 g  ·  Fat 7 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Steamed Rice Cake: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="33">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3867,7 +5367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3879,7 +5379,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Coconut Ladoo</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Coconut Ladoo</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3889,7 +5389,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Sweet  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3909,44 +5409,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 5 min · Cook 10 min</t>
         </is>
       </c>
     </row>
@@ -4094,13 +5594,13 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Cook coconut and jaggery in a steel pan 6–8 minutes until the mix holds together.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
@@ -4112,29 +5612,208 @@
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>Add cardamom. Shape 12 ladoos. Cool.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C21" s="31" t="n"/>
       <c r="D21" s="31" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Cook coconut and jaggery in a steel pan 6–8 minutes until the mix holds together.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Add cardamom. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Shape 12 ladoos. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cool. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 298  ·  Protein 2 g  ·  Carbs 37 g  ·  Fat 17 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Coconut Ladoo: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4148,7 +5827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4160,7 +5839,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chak-Hao Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chak-Hao Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4170,7 +5849,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Dessert  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4190,44 +5869,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 10 min · Cook 45 min</t>
         </is>
       </c>
     </row>
@@ -4393,61 +6072,253 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Drain rice. Simmer in milk in a heavy steel pot, stirring often, 35–40 minutes until thick.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>Add sugar and cardamom. Cook 5 minutes more.</t>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
         </is>
       </c>
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="31" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Serve warm or chilled, topped with pistachio. Never aluminium — milk reacts.</t>
+          <t>Drain rice. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Simmer in milk in a heavy steel pot, stirring often, 35–40 minutes until thick. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Add sugar and cardamom. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook 5 minutes more. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Serve warm or chilled, topped with pistachio. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Never aluminium — milk reacts. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 324  ·  Protein 10 g  ·  Carbs 49 g  ·  Fat 10 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Tree nuts · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Chak-Hao Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Tree nuts; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="33">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4725,7 +6596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4737,7 +6608,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  White Rice Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · White Rice Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4747,7 +6618,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Dessert  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4767,44 +6638,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 10 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -4970,48 +6841,227 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Simmer rice in milk in a steel pot until the grains burst and the milk is creamy, 30 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>Add sugar, cardamom and raisins. Cook 5 minutes. Serve warm.</t>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
         </is>
       </c>
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="31" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Simmer rice in milk in a steel pot until the grains burst and the milk is creamy, 30 minutes.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Add sugar, cardamom and raisins. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Cook 5 minutes. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Serve warm. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 314  ·  Protein 10 g  ·  Carbs 49 g  ·  Fat 9 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For White Rice Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5025,7 +7075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5037,7 +7087,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Yogurt with Honey</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Yogurt with Honey</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5047,7 +7097,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Dessert  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5067,44 +7117,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>Prep 5 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5234,13 +7284,13 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Spoon yogurt into 4 steel or glass bowls.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
@@ -5252,28 +7302,207 @@
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>Drizzle honey. Scatter sesame. Serve at once.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C20" s="31" t="n"/>
       <c r="D20" s="31" t="n"/>
     </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Spoon yogurt into 4 steel or glass bowls. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Drizzle honey. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Scatter sesame. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Serve at once. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 102  ·  Protein 4 g  ·  Carbs 11 g  ·  Fat 5 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Yogurt with Honey: keep it cold and set before service. Never store yogurt or milk sweets in aluminium. Garnish nuts only if the allergen card allows. Read spice and hing labels if used.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="29">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5287,7 +7516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5299,7 +7528,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Veg Singju</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Veg Singju</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5309,7 +7538,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Salad  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5329,44 +7558,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 15 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5568,50 +7797,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Toss cabbage and beans with sesame, roasted besan, chilli, lemon and salt.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>Rest 5 minutes so the besan clings. Serve the same hour — it weeps if it sits.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C24" s="31" t="n"/>
       <c r="D24" s="31" t="n"/>
     </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Toss cabbage and beans with sesame, roasted besan, chilli, lemon and salt. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Rest 5 minutes so the besan clings. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Serve the same hour — it weeps if it sits. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 147  ·  Protein 8 g  ·  Carbs 22 g  ·  Fat 4 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Veg Singju: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5625,7 +8020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5637,7 +8032,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cucumber Chilli Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cucumber Chilli Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5647,7 +8042,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Salad  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5667,44 +8062,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>Prep 6 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5852,34 +8247,200 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Toss cucumber, chilli, lemon and salt. Serve immediately.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Toss cucumber, chilli, lemon and salt. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Serve immediately. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 15  ·  Protein 1 g  ·  Carbs 4 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Cucumber Chilli Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5893,7 +8454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5905,7 +8466,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cabbage Lemon Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cabbage Lemon Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5915,7 +8476,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Salad  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5935,44 +8496,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -6120,34 +8681,200 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Toss cabbage with lemon, sesame and salt. Serve crisp and cold.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Toss cabbage with lemon, sesame and salt. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Serve crisp and cold. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 42  ·  Protein 2 g  ·  Carbs 6 g  ·  Fat 2 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Cabbage Lemon Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9386,7 +12113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9398,7 +12125,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Paknam Slices</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Paknam Slices</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9408,7 +12135,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Starter  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9428,44 +12155,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -9703,65 +12430,270 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Mix besan, water, ginger, chilli, coriander, salt, hing and mustard oil to a thick cake batter.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B26" s="30" t="inlineStr">
         <is>
-          <t>Line a steel steamer thali with the banana leaf. Pour in the batter 2 cm thick.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C26" s="31" t="n"/>
       <c r="D26" s="31" t="n"/>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="54" customHeight="1">
       <c r="A27" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B27" s="48" t="inlineStr">
         <is>
-          <t>Steam 20 minutes. Cool 5 minutes, turn out and slice into 8 fingers. Serve warm.</t>
+          <t>Heat fat in Stainless steel steamer and steel thali — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
         </is>
       </c>
       <c r="C27" s="49" t="n"/>
       <c r="D27" s="49" t="n"/>
     </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Mix besan, water, ginger, chilli, coriander, salt, hing and mustard oil to a thick cake batter.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="66" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Line a steel steamer thali with the banana leaf. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Pour in the batter 2 cm thick. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Steam 20 minutes. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="66" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Cool 5 minutes, turn out and slice into 8 fingers. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Serve warm. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="n"/>
+      <c r="D35" s="49" t="n"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>kcal 218  ·  Protein 9 g  ·  Carbs 31 g  ·  Fat 6 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>For Paknam Slices: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B44" s="52" t="n"/>
+      <c r="C44" s="52" t="n"/>
+      <c r="D44" s="52" t="n"/>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B45" s="50" t="n"/>
+      <c r="C45" s="50" t="n"/>
+      <c r="D45" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="38">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9775,7 +12707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9787,7 +12719,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kanghou Mixed Veg</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kanghou Mixed Veg</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9797,7 +12729,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Starter  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9817,44 +12749,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -10056,63 +12988,255 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Heat mustard oil in a steel kadhai until it just smokes, then lower the flame.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>Add ginger and chilli, then cabbage, beans and carrot. Stir-fry 8–10 minutes.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C24" s="31" t="n"/>
       <c r="D24" s="31" t="n"/>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Season with salt. Vegetables should stay bright, not soggy. Serve at once.</t>
+          <t>Heat mustard oil in a steel kadhai until it just smokes, then lower the flame. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Add ginger and chilli, then cabbage, beans and carrot. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Stir-fry 8–10 minutes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Season with salt. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Vegetables should stay bright, not soggy. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Serve at once. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 170  ·  Protein 6 g  ·  Carbs 21 g  ·  Fat 8 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Kanghou Mixed Veg: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="35">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10126,7 +13250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10138,7 +13262,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kangsoi Cup</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kangsoi Cup</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10148,7 +13272,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Starter  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10168,44 +13292,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10407,13 +13531,13 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Bring water, ginger and chilli to a boil in a stainless steel pot.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
@@ -10425,42 +13549,221 @@
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>Add cabbage, potato, beans and salt. Simmer 12 minutes until just tender.</t>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
         </is>
       </c>
       <c r="C24" s="31" t="n"/>
       <c r="D24" s="31" t="n"/>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Ladle into steel cups. Broth should be light and peppery, never cloudy from stock cubes.</t>
+          <t>Bring water, ginger and chilli to a boil in a stainless steel pot. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Add cabbage, potato, beans and salt. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Simmer 12 minutes until just tender. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Ladle into steel cups. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="66" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Broth should be light and peppery, never cloudy from stock cubes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 97  ·  Protein 5 g  ·  Carbs 19 g  ·  Fat 0 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Kangsoi Cup: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="34">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
@@ -10477,7 +13780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10489,7 +13792,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chamthong Stew</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chamthong Stew</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10499,7 +13802,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Main  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10519,44 +13822,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -10812,13 +14115,13 @@
       <c r="C25" s="46" t="n"/>
       <c r="D25" s="46" t="n"/>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="66" customHeight="1">
       <c r="A26" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Put water, ginger and chilli in a stainless steel pot and bring to a rolling boil.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C26" s="49" t="n"/>
@@ -10830,7 +14133,7 @@
       </c>
       <c r="B27" s="30" t="inlineStr">
         <is>
-          <t>Add potato and pumpkin first; cook 8 minutes. Add cabbage, carrot and beans.</t>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
         </is>
       </c>
       <c r="C27" s="31" t="n"/>
@@ -10842,49 +14145,254 @@
       </c>
       <c r="B28" s="48" t="inlineStr">
         <is>
-          <t>Season with salt. Simmer until all vegetables are tender but hold their shape, about 12 minutes more.</t>
+          <t>Put water, ginger and chilli in a stainless steel pot and bring to a rolling boil.</t>
         </is>
       </c>
       <c r="C28" s="49" t="n"/>
       <c r="D28" s="49" t="n"/>
     </row>
-    <row r="29" ht="42" customHeight="1">
+    <row r="29" ht="54" customHeight="1">
       <c r="A29" s="32" t="n">
         <v>4</v>
       </c>
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>Finish with coriander. Serve in steel bowls with sticky rice. Never aluminium.</t>
+          <t>Add potato and pumpkin first; cook 8 minutes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C29" s="31" t="n"/>
       <c r="D29" s="31" t="n"/>
     </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Add cabbage, carrot and beans. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Season with salt. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Simmer until all vegetables are tender but hold their shape, about 12 minutes more.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Finish with coriander. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>Serve in steel bowls with sticky rice. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Never aluminium. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="n"/>
+      <c r="D38" s="49" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>kcal 147  ·  Protein 7 g  ·  Carbs 30 g  ·  Fat 1 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="48" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+    </row>
+    <row r="45" ht="72" customHeight="1">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>For Chamthong Stew: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="n"/>
+      <c r="C45" s="26" t="n"/>
+      <c r="D45" s="26" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B46" s="52" t="n"/>
+      <c r="C46" s="52" t="n"/>
+      <c r="D46" s="52" t="n"/>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B47" s="50" t="n"/>
+      <c r="C47" s="50" t="n"/>
+      <c r="D47" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="40">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B37:D37"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10898,7 +14406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10910,7 +14418,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ooti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ooti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10920,7 +14428,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Main  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10940,44 +14448,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 15 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -11197,64 +14705,282 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Drain the peas. Cook with water, ginger, chilli and soda in a clay or steel pot until very soft, 30 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>Mash a ladle of peas against the pot. Stir in optional rice. Season with salt.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C25" s="31" t="n"/>
       <c r="D25" s="31" t="n"/>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="54" customHeight="1">
       <c r="A26" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Finish with mustard oil. The stew should be creamy, not watery. Serve with sticky rice.</t>
+          <t>Drain the peas. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C26" s="49" t="n"/>
       <c r="D26" s="49" t="n"/>
     </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook with water, ginger, chilli and soda in a clay or steel pot until very soft, 30 minutes.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Mash a ladle of peas against the pot. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Stir in optional rice. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Season with salt. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Finish with mustard oil. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>The stew should be creamy, not watery. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Serve with sticky rice. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>kcal 93  ·  Protein 3 g  ·  Carbs 12 g  ·  Fat 4 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>For Ooti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B44" s="52" t="n"/>
+      <c r="C44" s="52" t="n"/>
+      <c r="D44" s="52" t="n"/>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B45" s="50" t="n"/>
+      <c r="C45" s="50" t="n"/>
+      <c r="D45" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="38">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -11268,7 +14994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11280,7 +15006,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Veg Kangsoi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Veg Kangsoi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11290,7 +15016,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Manipur kitchen  ·  Main  ·  Meitei vegetarian table</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Manipur  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -11310,44 +15036,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -11549,60 +15275,239 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Boil water with ginger and chilli. Add mixed vegetables and salt; simmer 15 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="42" customHeight="1">
       <c r="A24" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>Stir in greens for the last 4 minutes.</t>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
         </is>
       </c>
       <c r="C24" s="31" t="n"/>
       <c r="D24" s="31" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="54" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Off the heat, add lemon juice. Serve as a soupy main with rice.</t>
+          <t>Boil water with ginger and chilli. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Add mixed vegetables and salt; simmer 15 minutes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Stir in greens for the last 4 minutes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Off the heat, add lemon juice. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Serve as a soupy main with rice. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 113  ·  Protein 4 g  ·  Carbs 18 g  ·  Fat 4 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Veg Kangsoi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="34">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
